--- a/portfolio_content_master.xlsx
+++ b/portfolio_content_master.xlsx
@@ -4409,17 +4409,17 @@
       </c>
       <c r="C21" s="42" t="inlineStr">
         <is>
-          <t>© {year} Iris Shen</t>
+          <t>© {year} Iris Shen. All Rights Reserved.</t>
         </is>
       </c>
       <c r="D21" s="42" t="inlineStr">
         <is>
-          <t>© {year} Iris Shen</t>
+          <t>© {year} Iris Shen. All Rights Reserved.</t>
         </is>
       </c>
       <c r="E21" s="42" t="inlineStr">
         <is>
-          <t>© {year} Iris Shen</t>
+          <t>© {year} Iris Shen. All Rights Reserved.</t>
         </is>
       </c>
       <c r="F21" s="43" t="inlineStr">
@@ -8603,45 +8603,45 @@
       </c>
     </row>
     <row r="26" ht="15" customHeight="1" s="96">
-      <c r="A26" t="inlineStr">
+      <c r="A26" s="95" t="inlineStr">
         <is>
           <t>zhangyuan_museum</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
+      <c r="B26" s="95" t="inlineStr">
         <is>
           <t>gallery</t>
         </is>
       </c>
-      <c r="C26" t="n">
+      <c r="C26" s="95" t="n">
         <v>30</v>
       </c>
-      <c r="D26" t="inlineStr">
+      <c r="D26" s="95" t="inlineStr">
         <is>
           <t>diagram</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr">
+      <c r="E26" s="95" t="inlineStr">
         <is>
           <t>assets/img/zhangyuan/zhangyuan-ecosystem-diagram.svg</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr">
+      <c r="F26" s="95" t="inlineStr">
         <is>
           <t>Ecosystem Diagram</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr">
+      <c r="G26" s="95" t="inlineStr">
         <is>
           <t>エコシステム図</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr">
+      <c r="H26" s="95" t="inlineStr">
         <is>
           <t>生态系统图</t>
         </is>
       </c>
-      <c r="M26" t="inlineStr">
+      <c r="M26" s="95" t="inlineStr">
         <is>
           <t>Zhangyuan ecosystem diagram</t>
         </is>
